--- a/event_planner_forms/006_easter_meal_order_form--event_planner_forms.xlsx
+++ b/event_planner_forms/006_easter_meal_order_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>easter_meal_order_form</t>
+          <t>What's your easter meal order preference?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>main_course</t>
+          <t>main_course_page</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>main_course</t>
+          <t>Which main course would you like?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>side_dish</t>
+          <t>side_dish_page</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>side_dish</t>
+          <t>Which side dish would you like?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>holiday_dessert</t>
+          <t>holiday_dessert_page</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>holiday_dessert</t>
+          <t>Would you like a holiday dessert?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>special_occassion</t>
+          <t>contact_information_page</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>special_occassion</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_page</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Your Contact Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_page</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Your Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_page</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Your Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>address_page</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Your Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>special_request</t>
+          <t>special_request_page</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>special_request</t>
+          <t>Any Special Requests?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>easter_event_date_page</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>Event Date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>easter_event_time_page</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>Event Time</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,40 +791,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>easter</t>
+          <t>easter_day_page</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>easter_ประก</t>
+          <t>Easter Day</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>easter_date</t>
+          <t>easter_egg_page</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>easter_date</t>
+          <t>Easter Egg</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>easter_time</t>
+          <t>easter_bunny_page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>easter_time</t>
+          <t>Easter Bunny</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,223 +865,62 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>easter_day</t>
+          <t>easter_meal_page</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>easter_day</t>
+          <t>Easter Meal</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>easter_egg</t>
+          <t>easter_holiday_page</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>easter_egg</t>
+          <t>Easter Holiday</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>easter_bunny</t>
+          <t>easter_time_page</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>easter_bunny</t>
+          <t>Easter Time Page</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>easter_meal</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>easter_meal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>easter_holiday</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>easter_holiday</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>easter_day2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>easter_day2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>easter_time2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>prophets_time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>easter_date2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>easter_date</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>easter_egg2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>easter_egg</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>easter_bunny2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>easter_bunny</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,306 +965,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>main_course_choices</t>
+          <t>easter_meal_order_form_page1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ham</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ham</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>main_course_choices</t>
+          <t>easter_meal_order_form_page1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>lamb</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Lamb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>side_dish_choices</t>
+          <t>easter_meal_order_form_page1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>side_dish_choices</t>
+          <t>easter_meal_order_form_page1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>holiday_dessert_choices</t>
+          <t>main_course_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>roasted_chicken</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Roasted chicken</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>holiday_dessert_choices</t>
+          <t>main_course_page_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>grilled_salmon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Grilled salmon</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>special_occassion_choices</t>
+          <t>main_course_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>vegetarian_option</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Vegetarian option</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>special_occassion_choices</t>
+          <t>main_course_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>easter_choices</t>
+          <t>side_dish_page_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>mashed_potatoes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Mashed potatoes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>easter_choices</t>
+          <t>side_dish_page_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>steamed_broccoli</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Steamed broccoli</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>easter_day_choices</t>
+          <t>side_dish_page_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>salad</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Salad</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>easter_day_choices</t>
+          <t>side_dish_page_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>easter_meal_choices</t>
+          <t>holiday_dessert_page_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>easter_meal_choices</t>
+          <t>holiday_dessert_page_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>easter_holiday_choices</t>
+          <t>holiday_dessert_page_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>easter_holiday_choices</t>
+          <t>contact_information_page_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>by_phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>By phone</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>easter_day2_choices</t>
+          <t>contact_information_page_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>by_email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>By email</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>easter_day2_choices</t>
+          <t>contact_information_page_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>easter_day_page_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>easter_day_page_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>easter_day_page_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>easter_meal_page_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>easter_meal_page_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>easter_holiday_page_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>easter_holiday_page_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
